--- a/outputs/q3/q3_relay_sorties.xlsx
+++ b/outputs/q3/q3_relay_sorties.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中继架次" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中继架次'!$A$1:$AA$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中继架次'!$A$1:$AA$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -613,47 +613,47 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>R-COMP-01</t>
+          <t>R-COMP-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>81.00344048954707</v>
+        <v>62.53744048954707</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>261.0034404895471</v>
+        <v>242.5374404895471</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>435.9422252795861</v>
+        <v>417.4762252795861</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>780.979</v>
+        <v>762.5129999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>780.979</v>
+        <v>762.5129999999999</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>780.979</v>
+        <v>762.5129999999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>810.979</v>
+        <v>792.5129999999999</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>810.979</v>
+        <v>792.513</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1925.918</v>
+        <v>1925.668</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1925.918</v>
+        <v>1925.668</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>2270.954774720414</v>
+        <v>2270.704774720414</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>2504.206487773799</v>
+        <v>2503.956487773799</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>2804.206487773799</v>
+        <v>2803.956487773799</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>109.2038334</v>
@@ -664,7 +664,7 @@
       <c r="S2" s="2" t="n">
         <v>527.4551391601562</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" t="n">
         <v>300</v>
       </c>
       <c r="U2" s="2" t="n">
@@ -677,16 +677,16 @@
         <v>0.009166666666666667</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.3406758055555555</v>
+        <v>0.3462418055555555</v>
       </c>
       <c r="Y2" s="2" t="n">
         <v>0.1102200808134655</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.6324982830709728</v>
+        <v>0.6380642830709727</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.802344286540321</v>
+        <v>0.8006049115403211</v>
       </c>
     </row>
     <row r="3">
@@ -702,47 +702,47 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>R-COMP-02</t>
+          <t>R-COMP-05</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>109.8448991956604</v>
+        <v>107.0018991956604</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>289.8448991956604</v>
+        <v>287.0018991956604</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>433.5265581312073</v>
+        <v>430.6835581312072</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>810.2</v>
+        <v>807.357</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>810.2</v>
+        <v>807.357</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>810.2</v>
+        <v>807.357</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>840.2</v>
+        <v>837.357</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>840.2</v>
+        <v>837.357</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>3604.149</v>
+        <v>3556.62</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3604.149</v>
+        <v>3556.62</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>3980.822441868792</v>
+        <v>3933.293441868793</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>4172.397987116188</v>
+        <v>4124.868987116189</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>4472.397987116188</v>
+        <v>4424.868987116189</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>109.279931</v>
@@ -766,16 +766,16 @@
         <v>0.009166666666666667</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.8445399722222222</v>
+        <v>0.8308859166666667</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0.1203262383747532</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>1.145458405613868</v>
+        <v>1.131804350058313</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.6420442482456661</v>
+        <v>0.6463111406067772</v>
       </c>
     </row>
     <row r="4">
@@ -795,76 +795,76 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2882.501177057822</v>
+        <v>2803.957373689164</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3062.501177057822</v>
+        <v>2983.957373689164</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3187.730443415244</v>
+        <v>3101.378191255082</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>3564.149</v>
+        <v>3516.619999999999</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3564.149</v>
+        <v>3516.619999999999</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3564.149</v>
+        <v>3516.619999999999</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3594.149</v>
+        <v>3546.619999999999</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3594.149</v>
+        <v>3546.62</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>5178.351</v>
+        <v>5539.141</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5178.351</v>
+        <v>5539.141</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>5554.769556584756</v>
+        <v>5954.382808744917</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>5721.741911727985</v>
+        <v>6110.943898832808</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>6021.741911727985</v>
+        <v>6410.943898832808</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>109.2363506</v>
+        <v>109.2389554</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>23.05923958644987</v>
+        <v>23.0642504</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>328.6170654296875</v>
-      </c>
-      <c r="T4" s="2" t="n">
+        <v>297.3832702636719</v>
+      </c>
+      <c r="T4" t="n">
         <v>300</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>628.6170654296875</v>
+        <v>597.3832702636719</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.1647816534857389</v>
+        <v>0.1744065102374906</v>
       </c>
       <c r="W4" s="2" t="n">
         <v>0.009166666666666667</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.4840617222222222</v>
+        <v>0.608825861111111</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.1202448166867971</v>
+        <v>0.1326466889046264</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.7782548590614248</v>
+        <v>0.9250457269198947</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.7567953565433048</v>
+        <v>0.7109232103375329</v>
       </c>
     </row>
     <row r="5">
@@ -884,43 +884,43 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4479.752893111123</v>
+        <v>4513.587893111123</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4659.752893111123</v>
+        <v>4693.587893111123</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4807.101643416298</v>
+        <v>4840.936643416298</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>5138.351</v>
+        <v>5172.186</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>5138.351</v>
+        <v>5172.186</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>5138.351</v>
+        <v>5172.186</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5168.351</v>
+        <v>5202.186</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>5168.351</v>
+        <v>5202.186</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>6787.068</v>
+        <v>6447.53</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>6787.068</v>
+        <v>6447.53</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>7118.317356583701</v>
+        <v>6778.779356583701</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>7314.782356990602</v>
+        <v>6975.244356990602</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>7614.782356990602</v>
+        <v>7275.244356990602</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>109.2052968146341</v>
@@ -944,109 +944,20 @@
         <v>0.009166666666666667</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.4946079722222224</v>
+        <v>0.3805217777777778</v>
       </c>
       <c r="Y5" s="2" t="n">
         <v>0.1058157666864601</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.7678096354118646</v>
+        <v>0.65372344096742</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.7600594889337923</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Q3-R05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>R-COMP-05</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>6145.052240382385</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6325.052240382385</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>6421.918729029846</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>6643.026999999999</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>6643.026999999999</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>6643.026999999999</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>6673.026999999999</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>6673.027</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>6970.845</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>6970.845</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>7191.953270970153</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>7321.108589166768</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>7621.108589166768</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>109.2213944</v>
-      </c>
-      <c r="R6" s="2" t="n">
-        <v>23.0371501</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>215.1659545898438</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>515.1659545898438</v>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>0.1050816392543911</v>
-      </c>
-      <c r="W6" s="2" t="n">
-        <v>0.009166666666666667</v>
-      </c>
-      <c r="X6" s="2" t="n">
-        <v>0.09099994444444451</v>
-      </c>
-      <c r="Y6" s="2" t="n">
-        <v>0.07063180878213236</v>
-      </c>
-      <c r="Z6" s="2" t="n">
-        <v>0.2758800591476346</v>
-      </c>
-      <c r="AA6" s="2" t="n">
-        <v>0.9137874815163642</v>
+        <v>0.7957114246976813</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA6"/>
+  <autoFilter ref="A1:AA5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>